--- a/xls/square_12_tri3_25.xlsx
+++ b/xls/square_12_tri3_25.xlsx
@@ -482,13 +482,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-0.0003383521207551709</v>
+        <v>-0.000338352120632075</v>
       </c>
       <c r="J25">
-        <v>-0.00023619776010724088</v>
+        <v>-0.0002361977600271099</v>
       </c>
       <c r="K25">
-        <v>2.4784894551026713</v>
+        <v>2.478489454872605</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -517,13 +517,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.00013130031359869952</v>
+        <v>-0.00013130031359030733</v>
       </c>
       <c r="J26">
-        <v>-0.00010134242696654746</v>
+        <v>-0.00010134242696133888</v>
       </c>
       <c r="K26">
-        <v>2.3574433311294665</v>
+        <v>2.357443331168706</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -552,13 +552,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-0.00012728293535512687</v>
+        <v>-0.00012728293537740936</v>
       </c>
       <c r="J27">
-        <v>-0.00010100184914905128</v>
+        <v>-0.00010100184916043299</v>
       </c>
       <c r="K27">
-        <v>2.369216451781241</v>
+        <v>2.3692164519817007</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -587,13 +587,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-0.00010517098693239281</v>
+        <v>-0.00010517098694102563</v>
       </c>
       <c r="J28">
-        <v>-7.895706854020371e-5</v>
+        <v>-7.895706854541202e-5</v>
       </c>
       <c r="K28">
-        <v>2.294947223759739</v>
+        <v>2.294947223812593</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -622,13 +622,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-9.211348458916951e-5</v>
+        <v>-9.211348457079517e-5</v>
       </c>
       <c r="J29">
-        <v>-6.877753921555717e-5</v>
+        <v>-6.877753920543014e-5</v>
       </c>
       <c r="K29">
-        <v>2.25647347508773</v>
+        <v>2.256473475098854</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -657,13 +657,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-9.10316434568388e-5</v>
+        <v>-9.103164344164746e-5</v>
       </c>
       <c r="J30">
-        <v>-7.031407680878037e-5</v>
+        <v>-7.03140768008716e-5</v>
       </c>
       <c r="K30">
-        <v>2.2745443055663115</v>
+        <v>2.274544305620989</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -692,13 +692,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-8.314256947326139e-5</v>
+        <v>-8.314256947388832e-5</v>
       </c>
       <c r="J31">
-        <v>-6.405283175619524e-5</v>
+        <v>-6.405283175638813e-5</v>
       </c>
       <c r="K31">
-        <v>2.2567535254004145</v>
+        <v>2.256753525565506</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -727,13 +727,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-8.14988123511796e-5</v>
+        <v>-8.149881236622592e-5</v>
       </c>
       <c r="J32">
-        <v>-6.157870010549524e-5</v>
+        <v>-6.15787001151881e-5</v>
       </c>
       <c r="K32">
-        <v>2.2384278686095653</v>
+        <v>2.2384278684321575</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_25.xlsx
+++ b/xls/square_12_tri3_25.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>676</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>169</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>576</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23">
+        <v>3174</v>
+      </c>
+      <c r="I23">
+        <v>-0.811767371559352</v>
+      </c>
+      <c r="J23">
+        <v>-0.5397852384853079</v>
+      </c>
+      <c r="K23">
+        <v>3.6138572199033407</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24">
+        <v>676</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>169</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>625</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24">
+        <v>3456</v>
+      </c>
+      <c r="I24">
+        <v>0.0025734810801766174</v>
+      </c>
+      <c r="J24">
+        <v>0.0008222159698810916</v>
+      </c>
+      <c r="K24">
+        <v>2.787298407012995</v>
+      </c>
+    </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
         <v>11</v>
